--- a/AI_기획서/샘플_체력회복시스템.xlsx
+++ b/AI_기획서/샘플_체력회복시스템.xlsx
@@ -18,7 +18,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="6">
+  <fonts count="5">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -28,31 +28,25 @@
     </font>
     <font>
       <name val="맑은 고딕"/>
+      <color rgb="FFFFFFFF"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="맑은 고딕"/>
       <b val="1"/>
-      <color theme="0"/>
+      <color rgb="FFFFFFFF"/>
       <sz val="14"/>
     </font>
     <font>
       <name val="맑은 고딕"/>
       <b val="1"/>
-      <color theme="0"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="맑은 고딕"/>
-      <color theme="0"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="맑은 고딕"/>
-      <b val="1"/>
-      <color theme="0"/>
+      <color rgb="FFFFFFFF"/>
       <sz val="15"/>
     </font>
     <font>
       <name val="맑은 고딕"/>
       <b val="1"/>
-      <color theme="0"/>
+      <color rgb="FFFFFFFF"/>
       <sz val="13"/>
     </font>
   </fonts>
@@ -65,12 +59,14 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="1"/>
+        <fgColor rgb="FF262626"/>
+        <bgColor rgb="FF262626"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="1" tint="0.1499984740745262"/>
+        <fgColor rgb="FF000000"/>
+        <bgColor rgb="FF000000"/>
       </patternFill>
     </fill>
   </fills>
@@ -86,27 +82,24 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -474,383 +467,781 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:H58"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <dimension ref="A1:H60"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="2.625" defaultRowHeight="16.5"/>
   <cols>
     <col width="2.625" customWidth="1" min="1" max="1"/>
     <col width="2.625" customWidth="1" min="3" max="3"/>
     <col width="2.625" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="n"/>
+      <c r="B1" s="1" t="n"/>
+      <c r="C1" s="1" t="n"/>
+      <c r="D1" s="1" t="n"/>
+      <c r="E1" s="1" t="n"/>
+      <c r="F1" s="1" t="n"/>
+      <c r="G1" s="1" t="n"/>
+      <c r="H1" s="1" t="n"/>
+    </row>
     <row r="2" ht="20.25" customHeight="1">
-      <c r="B2" s="1" t="inlineStr">
+      <c r="A2" s="2" t="n"/>
+      <c r="B2" s="3" t="inlineStr">
         <is>
           <t>목차</t>
         </is>
       </c>
       <c r="C2" s="2" t="n"/>
+      <c r="D2" s="2" t="n"/>
+      <c r="E2" s="2" t="n"/>
+      <c r="F2" s="2" t="n"/>
+      <c r="G2" s="2" t="n"/>
+      <c r="H2" s="2" t="n"/>
     </row>
     <row r="3" ht="20.25" customHeight="1">
-      <c r="B3" s="3" t="n"/>
+      <c r="A3" s="1" t="n"/>
+      <c r="B3" s="4" t="n"/>
+      <c r="C3" s="1" t="n"/>
+      <c r="D3" s="1" t="n"/>
+      <c r="E3" s="1" t="n"/>
+      <c r="F3" s="1" t="n"/>
+      <c r="G3" s="1" t="n"/>
+      <c r="H3" s="1" t="n"/>
     </row>
     <row r="4">
-      <c r="B4" s="4" t="inlineStr">
+      <c r="A4" s="1" t="n"/>
+      <c r="B4" s="1" t="inlineStr">
         <is>
           <t>1. 개요</t>
         </is>
       </c>
+      <c r="C4" s="1" t="n"/>
+      <c r="D4" s="1" t="n"/>
+      <c r="E4" s="1" t="n"/>
+      <c r="F4" s="1" t="n"/>
+      <c r="G4" s="1" t="n"/>
+      <c r="H4" s="1" t="n"/>
     </row>
     <row r="5">
-      <c r="C5" s="4" t="inlineStr">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="1" t="n"/>
+      <c r="C5" s="1" t="inlineStr">
         <is>
           <t>(1) 체력 회복이란</t>
         </is>
       </c>
+      <c r="D5" s="1" t="n"/>
+      <c r="E5" s="1" t="n"/>
+      <c r="F5" s="1" t="n"/>
+      <c r="G5" s="1" t="n"/>
+      <c r="H5" s="1" t="n"/>
     </row>
     <row r="6">
-      <c r="C6" s="4" t="inlineStr">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="1" t="n"/>
+      <c r="C6" s="1" t="inlineStr">
         <is>
           <t>(2) 회복 수단 종류</t>
         </is>
       </c>
+      <c r="D6" s="1" t="n"/>
+      <c r="E6" s="1" t="n"/>
+      <c r="F6" s="1" t="n"/>
+      <c r="G6" s="1" t="n"/>
+      <c r="H6" s="1" t="n"/>
     </row>
     <row r="7">
-      <c r="C7" s="4" t="n"/>
+      <c r="A7" s="1" t="n"/>
+      <c r="B7" s="1" t="n"/>
+      <c r="C7" s="1" t="n"/>
+      <c r="D7" s="1" t="n"/>
+      <c r="E7" s="1" t="n"/>
+      <c r="F7" s="1" t="n"/>
+      <c r="G7" s="1" t="n"/>
+      <c r="H7" s="1" t="n"/>
     </row>
     <row r="8">
-      <c r="B8" s="4" t="inlineStr">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="1" t="inlineStr">
         <is>
           <t>2. 회복 규칙</t>
         </is>
       </c>
+      <c r="C8" s="1" t="n"/>
+      <c r="D8" s="1" t="n"/>
+      <c r="E8" s="1" t="n"/>
+      <c r="F8" s="1" t="n"/>
+      <c r="G8" s="1" t="n"/>
+      <c r="H8" s="1" t="n"/>
     </row>
     <row r="9">
-      <c r="C9" s="4" t="inlineStr">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="1" t="n"/>
+      <c r="C9" s="1" t="inlineStr">
         <is>
           <t>(1) 즉시 회복</t>
         </is>
       </c>
+      <c r="D9" s="1" t="n"/>
+      <c r="E9" s="1" t="n"/>
+      <c r="F9" s="1" t="n"/>
+      <c r="G9" s="1" t="n"/>
+      <c r="H9" s="1" t="n"/>
     </row>
     <row r="10">
-      <c r="C10" s="4" t="inlineStr">
+      <c r="A10" s="1" t="n"/>
+      <c r="B10" s="1" t="n"/>
+      <c r="C10" s="1" t="inlineStr">
         <is>
           <t>(2) 지속 회복</t>
         </is>
       </c>
+      <c r="D10" s="1" t="n"/>
+      <c r="E10" s="1" t="n"/>
+      <c r="F10" s="1" t="n"/>
+      <c r="G10" s="1" t="n"/>
+      <c r="H10" s="1" t="n"/>
     </row>
     <row r="11">
-      <c r="C11" s="4" t="n"/>
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="1" t="n"/>
+      <c r="C11" s="1" t="n"/>
+      <c r="D11" s="1" t="n"/>
+      <c r="E11" s="1" t="n"/>
+      <c r="F11" s="1" t="n"/>
+      <c r="G11" s="1" t="n"/>
+      <c r="H11" s="1" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="1" t="n"/>
+      <c r="C12" s="1" t="n"/>
+      <c r="D12" s="1" t="n"/>
+      <c r="E12" s="1" t="n"/>
+      <c r="F12" s="1" t="n"/>
+      <c r="G12" s="1" t="n"/>
+      <c r="H12" s="1" t="n"/>
     </row>
     <row r="13" ht="24" customHeight="1">
+      <c r="A13" s="2" t="n"/>
       <c r="B13" s="5" t="inlineStr">
         <is>
           <t>1. 개요</t>
         </is>
       </c>
       <c r="C13" s="2" t="n"/>
+      <c r="D13" s="2" t="n"/>
+      <c r="E13" s="2" t="n"/>
+      <c r="F13" s="2" t="n"/>
+      <c r="G13" s="2" t="n"/>
+      <c r="H13" s="2" t="n"/>
     </row>
     <row r="14" ht="20.25" customHeight="1">
-      <c r="B14" s="3" t="n"/>
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="4" t="n"/>
+      <c r="C14" s="1" t="n"/>
+      <c r="D14" s="1" t="n"/>
+      <c r="E14" s="1" t="n"/>
+      <c r="F14" s="1" t="n"/>
+      <c r="G14" s="1" t="n"/>
+      <c r="H14" s="1" t="n"/>
     </row>
     <row r="15" ht="19.5" customHeight="1">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="1" t="n"/>
       <c r="C15" s="6" t="inlineStr">
         <is>
           <t>(1) 체력 회복이란</t>
         </is>
       </c>
+      <c r="D15" s="1" t="n"/>
+      <c r="E15" s="1" t="n"/>
+      <c r="F15" s="1" t="n"/>
+      <c r="G15" s="1" t="n"/>
+      <c r="H15" s="1" t="n"/>
     </row>
     <row r="16">
-      <c r="C16" s="4" t="n"/>
-      <c r="D16" s="4" t="inlineStr">
+      <c r="A16" s="1" t="n"/>
+      <c r="B16" s="1" t="n"/>
+      <c r="C16" s="1" t="n"/>
+      <c r="D16" s="1" t="inlineStr">
         <is>
           <t>A. 전투 중 줄어든 체력을 되돌리는 모든 행위를 뜻한다</t>
         </is>
       </c>
+      <c r="E16" s="1" t="n"/>
+      <c r="F16" s="1" t="n"/>
+      <c r="G16" s="1" t="n"/>
+      <c r="H16" s="1" t="n"/>
     </row>
     <row r="17">
-      <c r="C17" s="4" t="n"/>
-      <c r="E17" s="4" t="inlineStr">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="1" t="n"/>
+      <c r="C17" s="1" t="n"/>
+      <c r="D17" s="1" t="n"/>
+      <c r="E17" s="1" t="inlineStr">
         <is>
           <t>1) 아이템 사용, 스킬 발동, 환경 상호작용 등이 포함된다</t>
         </is>
       </c>
+      <c r="F17" s="1" t="n"/>
+      <c r="G17" s="1" t="n"/>
+      <c r="H17" s="1" t="n"/>
     </row>
     <row r="18">
-      <c r="C18" s="4" t="n"/>
-      <c r="E18" s="4" t="inlineStr">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="1" t="n"/>
+      <c r="C18" s="1" t="n"/>
+      <c r="D18" s="1" t="n"/>
+      <c r="E18" s="1" t="inlineStr">
         <is>
           <t>2) 회복량은 최대 체력을 넘지 않는다</t>
         </is>
       </c>
+      <c r="F18" s="1" t="n"/>
+      <c r="G18" s="1" t="n"/>
+      <c r="H18" s="1" t="n"/>
     </row>
     <row r="19">
-      <c r="C19" s="4" t="n"/>
+      <c r="A19" s="1" t="n"/>
+      <c r="B19" s="1" t="n"/>
+      <c r="C19" s="1" t="n"/>
+      <c r="D19" s="1" t="n"/>
+      <c r="E19" s="1" t="n"/>
+      <c r="F19" s="1" t="n"/>
+      <c r="G19" s="1" t="n"/>
+      <c r="H19" s="1" t="n"/>
     </row>
     <row r="20" ht="19.5" customHeight="1">
+      <c r="A20" s="1" t="n"/>
+      <c r="B20" s="1" t="n"/>
       <c r="C20" s="6" t="inlineStr">
         <is>
           <t>(2) 회복 수단 종류</t>
         </is>
       </c>
+      <c r="D20" s="1" t="n"/>
+      <c r="E20" s="1" t="n"/>
+      <c r="F20" s="1" t="n"/>
+      <c r="G20" s="1" t="n"/>
+      <c r="H20" s="1" t="n"/>
     </row>
     <row r="21">
-      <c r="C21" s="4" t="n"/>
-      <c r="D21" s="4" t="inlineStr">
+      <c r="A21" s="1" t="n"/>
+      <c r="B21" s="1" t="n"/>
+      <c r="C21" s="1" t="n"/>
+      <c r="D21" s="1" t="inlineStr">
         <is>
           <t>A. 즉시 회복</t>
         </is>
       </c>
+      <c r="E21" s="1" t="n"/>
+      <c r="F21" s="1" t="n"/>
+      <c r="G21" s="1" t="n"/>
+      <c r="H21" s="1" t="n"/>
     </row>
     <row r="22">
-      <c r="C22" s="4" t="n"/>
-      <c r="E22" s="4" t="inlineStr">
+      <c r="A22" s="1" t="n"/>
+      <c r="B22" s="1" t="n"/>
+      <c r="C22" s="1" t="n"/>
+      <c r="D22" s="1" t="n"/>
+      <c r="E22" s="1" t="inlineStr">
         <is>
           <t>1) 사용하면 곧바로 고정된 양만큼 체력을 돌려받는다</t>
         </is>
       </c>
+      <c r="F22" s="1" t="n"/>
+      <c r="G22" s="1" t="n"/>
+      <c r="H22" s="1" t="n"/>
     </row>
     <row r="23">
-      <c r="C23" s="4" t="n"/>
-      <c r="F23" s="4" t="inlineStr">
+      <c r="A23" s="1" t="n"/>
+      <c r="B23" s="1" t="n"/>
+      <c r="C23" s="1" t="n"/>
+      <c r="D23" s="1" t="n"/>
+      <c r="E23" s="1" t="n"/>
+      <c r="F23" s="1" t="inlineStr">
         <is>
           <t>a. 회복 아이템 (포션 등)</t>
         </is>
       </c>
+      <c r="G23" s="1" t="n"/>
+      <c r="H23" s="1" t="n"/>
     </row>
     <row r="24">
-      <c r="C24" s="4" t="n"/>
-      <c r="F24" s="4" t="inlineStr">
+      <c r="A24" s="1" t="n"/>
+      <c r="B24" s="1" t="n"/>
+      <c r="C24" s="1" t="n"/>
+      <c r="D24" s="1" t="n"/>
+      <c r="E24" s="1" t="n"/>
+      <c r="F24" s="1" t="inlineStr">
         <is>
           <t>b. 동료 힐 스킬</t>
         </is>
       </c>
+      <c r="G24" s="1" t="n"/>
+      <c r="H24" s="1" t="n"/>
     </row>
     <row r="25">
-      <c r="C25" s="4" t="n"/>
+      <c r="A25" s="1" t="n"/>
+      <c r="B25" s="1" t="n"/>
+      <c r="C25" s="1" t="n"/>
+      <c r="D25" s="1" t="n"/>
+      <c r="E25" s="1" t="n"/>
+      <c r="F25" s="1" t="n"/>
+      <c r="G25" s="1" t="n"/>
+      <c r="H25" s="1" t="n"/>
     </row>
     <row r="26">
-      <c r="C26" s="4" t="n"/>
-      <c r="D26" s="4" t="inlineStr">
+      <c r="A26" s="1" t="n"/>
+      <c r="B26" s="1" t="n"/>
+      <c r="C26" s="1" t="n"/>
+      <c r="D26" s="1" t="inlineStr">
         <is>
           <t>B. 지속 회복</t>
         </is>
       </c>
+      <c r="E26" s="1" t="n"/>
+      <c r="F26" s="1" t="n"/>
+      <c r="G26" s="1" t="n"/>
+      <c r="H26" s="1" t="n"/>
     </row>
     <row r="27">
-      <c r="C27" s="4" t="n"/>
-      <c r="E27" s="4" t="inlineStr">
+      <c r="A27" s="1" t="n"/>
+      <c r="B27" s="1" t="n"/>
+      <c r="C27" s="1" t="n"/>
+      <c r="D27" s="1" t="n"/>
+      <c r="E27" s="1" t="inlineStr">
         <is>
           <t>1) 일정 시간 동안 조금씩 나눠서 체력을 돌려받는다</t>
         </is>
       </c>
+      <c r="F27" s="1" t="n"/>
+      <c r="G27" s="1" t="n"/>
+      <c r="H27" s="1" t="n"/>
     </row>
     <row r="28">
-      <c r="C28" s="4" t="n"/>
-      <c r="F28" s="4" t="inlineStr">
+      <c r="A28" s="1" t="n"/>
+      <c r="B28" s="1" t="n"/>
+      <c r="C28" s="1" t="n"/>
+      <c r="D28" s="1" t="n"/>
+      <c r="E28" s="1" t="n"/>
+      <c r="F28" s="1" t="inlineStr">
         <is>
           <t>a. 회복 음식 (서서히 회복)</t>
         </is>
       </c>
+      <c r="G28" s="1" t="n"/>
+      <c r="H28" s="1" t="n"/>
     </row>
     <row r="29">
-      <c r="C29" s="4" t="n"/>
-      <c r="F29" s="4" t="inlineStr">
+      <c r="A29" s="1" t="n"/>
+      <c r="B29" s="1" t="n"/>
+      <c r="C29" s="1" t="n"/>
+      <c r="D29" s="1" t="n"/>
+      <c r="E29" s="1" t="n"/>
+      <c r="F29" s="1" t="inlineStr">
         <is>
           <t>b. 휴식 장소 (모닥불, 웨이포인트)</t>
         </is>
       </c>
+      <c r="G29" s="1" t="n"/>
+      <c r="H29" s="1" t="n"/>
     </row>
     <row r="30">
-      <c r="C30" s="7" t="n"/>
-      <c r="G30" s="4" t="n"/>
+      <c r="A30" s="1" t="n"/>
+      <c r="B30" s="1" t="n"/>
+      <c r="C30" s="1" t="n"/>
+      <c r="D30" s="1" t="n"/>
+      <c r="E30" s="1" t="n"/>
+      <c r="F30" s="1" t="n"/>
+      <c r="G30" s="1" t="n"/>
+      <c r="H30" s="1" t="n"/>
     </row>
     <row r="31">
-      <c r="C31" s="7" t="n"/>
-      <c r="G31" s="4" t="n"/>
+      <c r="A31" s="1" t="n"/>
+      <c r="B31" s="1" t="n"/>
+      <c r="C31" s="1" t="n"/>
+      <c r="D31" s="1" t="n"/>
+      <c r="E31" s="1" t="n"/>
+      <c r="F31" s="1" t="n"/>
+      <c r="G31" s="1" t="n"/>
+      <c r="H31" s="1" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="1" t="n"/>
+      <c r="B32" s="1" t="n"/>
+      <c r="C32" s="1" t="n"/>
+      <c r="D32" s="1" t="n"/>
+      <c r="E32" s="1" t="n"/>
+      <c r="F32" s="1" t="n"/>
+      <c r="G32" s="1" t="n"/>
+      <c r="H32" s="1" t="n"/>
     </row>
     <row r="33" ht="20.25" customHeight="1">
-      <c r="B33" s="1" t="inlineStr">
+      <c r="A33" s="2" t="n"/>
+      <c r="B33" s="3" t="inlineStr">
         <is>
           <t>2. 회복 규칙</t>
         </is>
       </c>
       <c r="C33" s="2" t="n"/>
+      <c r="D33" s="2" t="n"/>
+      <c r="E33" s="2" t="n"/>
+      <c r="F33" s="2" t="n"/>
+      <c r="G33" s="2" t="n"/>
+      <c r="H33" s="2" t="n"/>
     </row>
     <row r="34" ht="20.25" customHeight="1">
-      <c r="B34" s="3" t="n"/>
+      <c r="A34" s="1" t="n"/>
+      <c r="B34" s="4" t="n"/>
+      <c r="C34" s="1" t="n"/>
+      <c r="D34" s="1" t="n"/>
+      <c r="E34" s="1" t="n"/>
+      <c r="F34" s="1" t="n"/>
+      <c r="G34" s="1" t="n"/>
+      <c r="H34" s="1" t="n"/>
     </row>
     <row r="35" ht="19.5" customHeight="1">
+      <c r="A35" s="1" t="n"/>
+      <c r="B35" s="1" t="n"/>
       <c r="C35" s="6" t="inlineStr">
         <is>
           <t>(1) 즉시 회복</t>
         </is>
       </c>
+      <c r="D35" s="1" t="n"/>
+      <c r="E35" s="1" t="n"/>
+      <c r="F35" s="1" t="n"/>
+      <c r="G35" s="1" t="n"/>
+      <c r="H35" s="1" t="n"/>
     </row>
     <row r="36">
-      <c r="C36" s="4" t="n"/>
-      <c r="D36" s="4" t="inlineStr">
+      <c r="A36" s="1" t="n"/>
+      <c r="B36" s="1" t="n"/>
+      <c r="C36" s="1" t="n"/>
+      <c r="D36" s="1" t="inlineStr">
         <is>
           <t>A. 기본 규칙</t>
         </is>
       </c>
+      <c r="E36" s="1" t="n"/>
+      <c r="F36" s="1" t="n"/>
+      <c r="G36" s="1" t="n"/>
+      <c r="H36" s="1" t="n"/>
     </row>
     <row r="37">
-      <c r="C37" s="4" t="n"/>
-      <c r="E37" s="4" t="inlineStr">
+      <c r="A37" s="1" t="n"/>
+      <c r="B37" s="1" t="n"/>
+      <c r="C37" s="1" t="n"/>
+      <c r="D37" s="1" t="n"/>
+      <c r="E37" s="1" t="inlineStr">
         <is>
           <t>1) 아이템 사용 시 DT_Item의 HealAmount만큼 즉시 회복된다</t>
         </is>
       </c>
+      <c r="F37" s="1" t="n"/>
+      <c r="G37" s="1" t="n"/>
+      <c r="H37" s="1" t="n"/>
     </row>
     <row r="38">
-      <c r="C38" s="4" t="n"/>
-      <c r="E38" s="4" t="inlineStr">
+      <c r="A38" s="1" t="n"/>
+      <c r="B38" s="1" t="n"/>
+      <c r="C38" s="1" t="n"/>
+      <c r="D38" s="1" t="n"/>
+      <c r="E38" s="1" t="inlineStr">
         <is>
           <t>2) 전투 중에도 사용할 수 있다</t>
         </is>
       </c>
+      <c r="F38" s="1" t="n"/>
+      <c r="G38" s="1" t="n"/>
+      <c r="H38" s="1" t="n"/>
     </row>
     <row r="39">
-      <c r="C39" s="4" t="n"/>
-      <c r="F39" s="4" t="inlineStr">
+      <c r="A39" s="1" t="n"/>
+      <c r="B39" s="1" t="n"/>
+      <c r="C39" s="1" t="n"/>
+      <c r="D39" s="1" t="n"/>
+      <c r="E39" s="1" t="n"/>
+      <c r="F39" s="1" t="inlineStr">
         <is>
           <t>a. 사용 모션 도중 피격 시 회복이 취소된다</t>
         </is>
       </c>
+      <c r="G39" s="1" t="n"/>
+      <c r="H39" s="1" t="n"/>
     </row>
     <row r="40">
-      <c r="C40" s="4" t="n"/>
-      <c r="F40" s="4" t="inlineStr">
+      <c r="A40" s="1" t="n"/>
+      <c r="B40" s="1" t="n"/>
+      <c r="C40" s="1" t="n"/>
+      <c r="D40" s="1" t="n"/>
+      <c r="E40" s="1" t="n"/>
+      <c r="F40" s="1" t="inlineStr">
         <is>
           <t>b. 쿨타임은 아이템마다 따로 적용된다</t>
         </is>
       </c>
+      <c r="G40" s="1" t="n"/>
+      <c r="H40" s="1" t="n"/>
     </row>
     <row r="41">
-      <c r="C41" s="4" t="n"/>
+      <c r="A41" s="1" t="n"/>
+      <c r="B41" s="1" t="n"/>
+      <c r="C41" s="1" t="n"/>
+      <c r="D41" s="1" t="n"/>
+      <c r="E41" s="1" t="n"/>
+      <c r="F41" s="1" t="n"/>
+      <c r="G41" s="1" t="n"/>
+      <c r="H41" s="1" t="n"/>
     </row>
     <row r="42">
-      <c r="C42" s="4" t="n"/>
-      <c r="D42" s="4" t="inlineStr">
+      <c r="A42" s="1" t="n"/>
+      <c r="B42" s="1" t="n"/>
+      <c r="C42" s="1" t="n"/>
+      <c r="D42" s="1" t="inlineStr">
         <is>
           <t>B. 동료 힐 스킬</t>
         </is>
       </c>
+      <c r="E42" s="1" t="n"/>
+      <c r="F42" s="1" t="n"/>
+      <c r="G42" s="1" t="n"/>
+      <c r="H42" s="1" t="n"/>
     </row>
     <row r="43">
-      <c r="C43" s="4" t="n"/>
-      <c r="E43" s="4" t="inlineStr">
+      <c r="A43" s="1" t="n"/>
+      <c r="B43" s="1" t="n"/>
+      <c r="C43" s="1" t="n"/>
+      <c r="D43" s="1" t="n"/>
+      <c r="E43" s="1" t="inlineStr">
         <is>
           <t>1) AI 동료가 리더 체력이 30% 이하일 때 자동으로 사용한다</t>
         </is>
       </c>
+      <c r="F43" s="1" t="n"/>
+      <c r="G43" s="1" t="n"/>
+      <c r="H43" s="1" t="n"/>
     </row>
     <row r="44">
-      <c r="C44" s="4" t="n"/>
-      <c r="F44" s="4" t="inlineStr">
+      <c r="A44" s="1" t="n"/>
+      <c r="B44" s="1" t="n"/>
+      <c r="C44" s="1" t="n"/>
+      <c r="D44" s="1" t="n"/>
+      <c r="E44" s="1" t="n"/>
+      <c r="F44" s="1" t="inlineStr">
         <is>
           <t>a. 동료 스킬 쿨타임이 적용된다</t>
         </is>
       </c>
+      <c r="G44" s="1" t="n"/>
+      <c r="H44" s="1" t="n"/>
     </row>
     <row r="45">
-      <c r="C45" s="4" t="n"/>
-      <c r="F45" s="4" t="inlineStr">
+      <c r="A45" s="1" t="n"/>
+      <c r="B45" s="1" t="n"/>
+      <c r="C45" s="1" t="n"/>
+      <c r="D45" s="1" t="n"/>
+      <c r="E45" s="1" t="n"/>
+      <c r="F45" s="1" t="inlineStr">
         <is>
           <t>b. 동료가 사망 중이면 사용할 수 없다</t>
         </is>
       </c>
+      <c r="G45" s="1" t="n"/>
+      <c r="H45" s="1" t="n"/>
     </row>
     <row r="46">
-      <c r="C46" s="7" t="n"/>
-      <c r="G46" s="4" t="n"/>
+      <c r="A46" s="1" t="n"/>
+      <c r="B46" s="1" t="n"/>
+      <c r="C46" s="1" t="n"/>
+      <c r="D46" s="1" t="n"/>
+      <c r="E46" s="1" t="n"/>
+      <c r="F46" s="1" t="n"/>
+      <c r="G46" s="1" t="n"/>
+      <c r="H46" s="1" t="n"/>
     </row>
     <row r="47" ht="19.5" customHeight="1">
+      <c r="A47" s="1" t="n"/>
+      <c r="B47" s="1" t="n"/>
       <c r="C47" s="6" t="inlineStr">
         <is>
           <t>(2) 지속 회복</t>
         </is>
       </c>
+      <c r="D47" s="1" t="n"/>
+      <c r="E47" s="1" t="n"/>
+      <c r="F47" s="1" t="n"/>
+      <c r="G47" s="1" t="n"/>
+      <c r="H47" s="1" t="n"/>
     </row>
     <row r="48">
-      <c r="C48" s="4" t="n"/>
-      <c r="D48" s="4" t="inlineStr">
+      <c r="A48" s="1" t="n"/>
+      <c r="B48" s="1" t="n"/>
+      <c r="C48" s="1" t="n"/>
+      <c r="D48" s="1" t="inlineStr">
         <is>
           <t>A. 틱 회복 규칙</t>
         </is>
       </c>
+      <c r="E48" s="1" t="n"/>
+      <c r="F48" s="1" t="n"/>
+      <c r="G48" s="1" t="n"/>
+      <c r="H48" s="1" t="n"/>
     </row>
     <row r="49">
-      <c r="C49" s="4" t="n"/>
-      <c r="E49" s="4" t="inlineStr">
+      <c r="A49" s="1" t="n"/>
+      <c r="B49" s="1" t="n"/>
+      <c r="C49" s="1" t="n"/>
+      <c r="D49" s="1" t="n"/>
+      <c r="E49" s="1" t="inlineStr">
         <is>
           <t>1) 1초 간격으로 HealPerTick만큼 회복된다</t>
         </is>
       </c>
+      <c r="F49" s="1" t="n"/>
+      <c r="G49" s="1" t="n"/>
+      <c r="H49" s="1" t="n"/>
     </row>
     <row r="50">
-      <c r="C50" s="4" t="n"/>
-      <c r="E50" s="4" t="inlineStr">
+      <c r="A50" s="1" t="n"/>
+      <c r="B50" s="1" t="n"/>
+      <c r="C50" s="1" t="n"/>
+      <c r="D50" s="1" t="n"/>
+      <c r="E50" s="1" t="inlineStr">
         <is>
           <t>2) 피격을 받아도 지속 회복은 끊기지 않는다</t>
         </is>
       </c>
+      <c r="F50" s="1" t="n"/>
+      <c r="G50" s="1" t="n"/>
+      <c r="H50" s="1" t="n"/>
     </row>
     <row r="51">
-      <c r="C51" s="4" t="n"/>
-      <c r="E51" s="4" t="inlineStr">
+      <c r="A51" s="1" t="n"/>
+      <c r="B51" s="1" t="n"/>
+      <c r="C51" s="1" t="n"/>
+      <c r="D51" s="1" t="n"/>
+      <c r="E51" s="1" t="inlineStr">
         <is>
           <t>3) 최대 체력에 도달하면 남은 회복은 사라진다</t>
         </is>
       </c>
+      <c r="F51" s="1" t="n"/>
+      <c r="G51" s="1" t="n"/>
+      <c r="H51" s="1" t="n"/>
     </row>
     <row r="52">
-      <c r="C52" s="4" t="n"/>
+      <c r="A52" s="1" t="n"/>
+      <c r="B52" s="1" t="n"/>
+      <c r="C52" s="1" t="n"/>
+      <c r="D52" s="1" t="n"/>
+      <c r="E52" s="1" t="n"/>
+      <c r="F52" s="1" t="n"/>
+      <c r="G52" s="1" t="n"/>
+      <c r="H52" s="1" t="n"/>
     </row>
     <row r="53">
-      <c r="C53" s="4" t="n"/>
-      <c r="D53" s="4" t="inlineStr">
+      <c r="A53" s="1" t="n"/>
+      <c r="B53" s="1" t="n"/>
+      <c r="C53" s="1" t="n"/>
+      <c r="D53" s="1" t="inlineStr">
         <is>
           <t>B. 휴식 회복</t>
         </is>
       </c>
+      <c r="E53" s="1" t="n"/>
+      <c r="F53" s="1" t="n"/>
+      <c r="G53" s="1" t="n"/>
+      <c r="H53" s="1" t="n"/>
     </row>
     <row r="54">
-      <c r="C54" s="4" t="n"/>
-      <c r="E54" s="4" t="inlineStr">
+      <c r="A54" s="1" t="n"/>
+      <c r="B54" s="1" t="n"/>
+      <c r="C54" s="1" t="n"/>
+      <c r="D54" s="1" t="n"/>
+      <c r="E54" s="1" t="inlineStr">
         <is>
           <t>1) 모닥불이나 웨이포인트에서 휴식하면 체력을 전부 돌려받는다</t>
         </is>
       </c>
+      <c r="F54" s="1" t="n"/>
+      <c r="G54" s="1" t="n"/>
+      <c r="H54" s="1" t="n"/>
     </row>
     <row r="55">
-      <c r="C55" s="4" t="n"/>
-      <c r="F55" s="4" t="inlineStr">
+      <c r="A55" s="1" t="n"/>
+      <c r="B55" s="1" t="n"/>
+      <c r="C55" s="1" t="n"/>
+      <c r="D55" s="1" t="n"/>
+      <c r="E55" s="1" t="n"/>
+      <c r="F55" s="1" t="inlineStr">
         <is>
           <t>a. 휴식을 시작하려면 먼저 전투 상태가 풀려야 한다</t>
         </is>
       </c>
+      <c r="G55" s="1" t="n"/>
+      <c r="H55" s="1" t="n"/>
     </row>
     <row r="56">
-      <c r="C56" s="7" t="n"/>
-      <c r="G56" s="4" t="inlineStr">
+      <c r="A56" s="1" t="n"/>
+      <c r="B56" s="1" t="n"/>
+      <c r="C56" s="1" t="n"/>
+      <c r="D56" s="1" t="n"/>
+      <c r="E56" s="1" t="n"/>
+      <c r="F56" s="1" t="n"/>
+      <c r="G56" s="1" t="inlineStr">
         <is>
           <t>- 근처에 적이 있으면 휴식을 시작할 수 없다</t>
         </is>
       </c>
+      <c r="H56" s="1" t="n"/>
     </row>
     <row r="57">
-      <c r="C57" s="7" t="n"/>
-      <c r="G57" s="4" t="n"/>
-      <c r="H57" s="4" t="inlineStr">
-        <is>
-          <t>주변에 위협이 남아 있습니다 메시지가 뜬다</t>
+      <c r="A57" s="1" t="n"/>
+      <c r="B57" s="1" t="n"/>
+      <c r="C57" s="1" t="n"/>
+      <c r="D57" s="1" t="n"/>
+      <c r="E57" s="1" t="n"/>
+      <c r="F57" s="1" t="n"/>
+      <c r="G57" s="1" t="n"/>
+      <c r="H57" s="1" t="inlineStr">
+        <is>
+          <t>· 주변에 위협이 남아 있습니다 메시지가 뜬다</t>
         </is>
       </c>
     </row>
     <row r="58">
-      <c r="C58" s="7" t="n"/>
-      <c r="G58" s="4" t="n"/>
+      <c r="A58" s="1" t="n"/>
+      <c r="B58" s="1" t="n"/>
+      <c r="C58" s="1" t="n"/>
+      <c r="D58" s="1" t="n"/>
+      <c r="E58" s="1" t="n"/>
+      <c r="F58" s="1" t="n"/>
+      <c r="G58" s="1" t="n"/>
+      <c r="H58" s="1" t="n"/>
+    </row>
+    <row r="59">
+      <c r="A59" s="1" t="n"/>
+      <c r="B59" s="1" t="n"/>
+      <c r="C59" s="1" t="n"/>
+      <c r="D59" s="1" t="n"/>
+      <c r="E59" s="1" t="n"/>
+      <c r="F59" s="1" t="n"/>
+      <c r="G59" s="1" t="n"/>
+      <c r="H59" s="1" t="n"/>
+    </row>
+    <row r="60">
+      <c r="A60" s="1" t="n"/>
+      <c r="B60" s="1" t="n"/>
+      <c r="C60" s="1" t="n"/>
+      <c r="D60" s="1" t="n"/>
+      <c r="E60" s="1" t="n"/>
+      <c r="F60" s="1" t="n"/>
+      <c r="G60" s="1" t="n"/>
+      <c r="H60" s="1" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -863,32 +1254,113 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B3:B5"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <dimension ref="A1:H9"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="2.625" defaultRowHeight="16.5"/>
   <cols>
     <col width="2.625" customWidth="1" min="1" max="1"/>
   </cols>
   <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="n"/>
+      <c r="B1" s="1" t="n"/>
+      <c r="C1" s="1" t="n"/>
+      <c r="D1" s="1" t="n"/>
+      <c r="E1" s="1" t="n"/>
+      <c r="F1" s="1" t="n"/>
+      <c r="G1" s="1" t="n"/>
+      <c r="H1" s="1" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="n"/>
+      <c r="B2" s="1" t="n"/>
+      <c r="C2" s="1" t="n"/>
+      <c r="D2" s="1" t="n"/>
+      <c r="E2" s="1" t="n"/>
+      <c r="F2" s="1" t="n"/>
+      <c r="G2" s="1" t="n"/>
+      <c r="H2" s="1" t="n"/>
+    </row>
     <row r="3">
-      <c r="B3" s="4" t="inlineStr">
+      <c r="A3" s="1" t="n"/>
+      <c r="B3" s="1" t="inlineStr">
         <is>
           <t>1. 중요한 내용은 bold 처리를 한다.</t>
         </is>
       </c>
+      <c r="C3" s="1" t="n"/>
+      <c r="D3" s="1" t="n"/>
+      <c r="E3" s="1" t="n"/>
+      <c r="F3" s="1" t="n"/>
+      <c r="G3" s="1" t="n"/>
+      <c r="H3" s="1" t="n"/>
     </row>
     <row r="4">
-      <c r="B4" s="4" t="inlineStr">
+      <c r="A4" s="1" t="n"/>
+      <c r="B4" s="1" t="inlineStr">
         <is>
           <t>2. 더 중요한 내용은 주황색 컬러로 텍스트를 칠한다.</t>
         </is>
       </c>
+      <c r="C4" s="1" t="n"/>
+      <c r="D4" s="1" t="n"/>
+      <c r="E4" s="1" t="n"/>
+      <c r="F4" s="1" t="n"/>
+      <c r="G4" s="1" t="n"/>
+      <c r="H4" s="1" t="n"/>
     </row>
     <row r="5">
-      <c r="B5" s="4" t="inlineStr">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="1" t="inlineStr">
         <is>
           <t>3. 가장 중요한 내용은 bold하고 주황색 컬러로 텍스트를 칠한다.</t>
         </is>
       </c>
+      <c r="C5" s="1" t="n"/>
+      <c r="D5" s="1" t="n"/>
+      <c r="E5" s="1" t="n"/>
+      <c r="F5" s="1" t="n"/>
+      <c r="G5" s="1" t="n"/>
+      <c r="H5" s="1" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="1" t="n"/>
+      <c r="C6" s="1" t="n"/>
+      <c r="D6" s="1" t="n"/>
+      <c r="E6" s="1" t="n"/>
+      <c r="F6" s="1" t="n"/>
+      <c r="G6" s="1" t="n"/>
+      <c r="H6" s="1" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="n"/>
+      <c r="B7" s="1" t="n"/>
+      <c r="C7" s="1" t="n"/>
+      <c r="D7" s="1" t="n"/>
+      <c r="E7" s="1" t="n"/>
+      <c r="F7" s="1" t="n"/>
+      <c r="G7" s="1" t="n"/>
+      <c r="H7" s="1" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="1" t="n"/>
+      <c r="C8" s="1" t="n"/>
+      <c r="D8" s="1" t="n"/>
+      <c r="E8" s="1" t="n"/>
+      <c r="F8" s="1" t="n"/>
+      <c r="G8" s="1" t="n"/>
+      <c r="H8" s="1" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="1" t="n"/>
+      <c r="C9" s="1" t="n"/>
+      <c r="D9" s="1" t="n"/>
+      <c r="E9" s="1" t="n"/>
+      <c r="F9" s="1" t="n"/>
+      <c r="G9" s="1" t="n"/>
+      <c r="H9" s="1" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
